--- a/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0001T0006Z000C1N19_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0001T0006Z000C1N19_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>27.40759285314035</v>
+        <v>4.453733838635307</v>
       </c>
       <c r="D2" t="n">
-        <v>29.02681332723597</v>
+        <v>4.716857165675845</v>
       </c>
       <c r="E2" t="n">
-        <v>5.057434593233816</v>
+        <v>0.8218331214004951</v>
       </c>
       <c r="F2" t="n">
-        <v>5.677222955885299</v>
+        <v>0.9225487303313613</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>15.63301157682223</v>
+        <v>2.540364381233613</v>
       </c>
       <c r="D3" t="n">
-        <v>15.79715809488322</v>
+        <v>2.567038190418522</v>
       </c>
       <c r="E3" t="n">
-        <v>5.057434593233816</v>
+        <v>0.8218331214004951</v>
       </c>
       <c r="F3" t="n">
-        <v>5.677222955885299</v>
+        <v>0.9225487303313613</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>18.18581157662202</v>
+        <v>2.955194381201079</v>
       </c>
       <c r="D4" t="n">
-        <v>18.70105064917146</v>
+        <v>3.038920730490362</v>
       </c>
       <c r="E4" t="n">
-        <v>5.057434593233816</v>
+        <v>0.8218331214004951</v>
       </c>
       <c r="F4" t="n">
-        <v>5.677222955885299</v>
+        <v>0.9225487303313613</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
